--- a/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T19:12:26+00:00</t>
+    <t>2024-11-21T03:15:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/feature/observateion_endoscopy.valueのバインディングをcodableconceptのみに適用する/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-21T03:15:21+00:00</t>
+    <t>2024-11-21T03:32:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
